--- a/data_ext/sources.xlsx
+++ b/data_ext/sources.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="735" windowWidth="12960" windowHeight="5865" tabRatio="831"/>
   </bookViews>
   <sheets>
     <sheet name="Quotas" sheetId="18" r:id="rId1"/>
@@ -58,7 +58,7 @@
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
 https://www.insee.fr/fr/statistiques/2381474
-Calcul : WOmen 18+ / Pop 18+
+Calcul : Men 18+ / Pop 18+
 </t>
         </r>
       </text>
@@ -75,7 +75,7 @@
           </rPr>
           <t xml:space="preserve">Source(year 2025) : INSEE
 https://www.insee.fr/fr/statistiques/2381474
-Calcul : Men 18+ / Pop 18+
+Calcul : WOmen 18+ / Pop 18+
 </t>
         </r>
       </text>
@@ -388,7 +388,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="184">
   <si>
     <t>Country</t>
   </si>
@@ -453,9 +453,6 @@
     <t>50-64</t>
   </si>
   <si>
-    <t>&gt;65</t>
-  </si>
-  <si>
     <t>Below upper secondary 25-64 0-2</t>
   </si>
   <si>
@@ -940,6 +937,9 @@
   </si>
   <si>
     <t>Autre</t>
+  </si>
+  <si>
+    <t>65+</t>
   </si>
 </sst>
 </file>
@@ -1381,8 +1381,8 @@
     <col min="13" max="13" width="5.85546875" customWidth="1"/>
     <col min="14" max="14" width="5.28515625" customWidth="1"/>
     <col min="15" max="15" width="5.42578125" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" customWidth="1"/>
-    <col min="17" max="17" width="5.5703125" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" customWidth="1"/>
     <col min="18" max="19" width="5" customWidth="1"/>
     <col min="20" max="20" width="4.5703125" customWidth="1"/>
     <col min="21" max="21" width="5.85546875" customWidth="1"/>
@@ -1413,19 +1413,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>17</v>
@@ -1440,64 +1440,64 @@
         <v>20</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="AE1" s="7" t="s">
         <v>6</v>
@@ -1521,73 +1521,73 @@
         <v>9</v>
       </c>
       <c r="AL1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AN1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AN1" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="AO1" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AR1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AS1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AT1" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AU1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AV1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AW1" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="AU1" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AX1" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="AY1" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AZ1" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="BA1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="BB1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="BC1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="BD1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="BE1" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="BF1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BG1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="BI1" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="AX1" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="AY1" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="AZ1" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="BA1" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="BB1" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="BC1" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="BD1" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="BE1" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="BF1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="BG1" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="BI1" s="11" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:64" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -1602,10 +1602,10 @@
         <v>798</v>
       </c>
       <c r="E2" s="16">
+        <v>478</v>
+      </c>
+      <c r="F2" s="16">
         <v>522</v>
-      </c>
-      <c r="F2" s="16">
-        <v>478</v>
       </c>
       <c r="G2" s="18">
         <v>104</v>
@@ -1623,25 +1623,25 @@
         <v>273</v>
       </c>
       <c r="L2" s="19">
-        <f t="shared" ref="L2:N2" si="0">AL2*SUM($H2:$J2)/100</f>
+        <f>AL2*SUM($H2:$J2)/100</f>
         <v>101.54899999999999</v>
       </c>
       <c r="M2" s="19">
-        <f t="shared" si="0"/>
+        <f>AM2*SUM($H2:$J2)/100</f>
         <v>256.67600000000004</v>
       </c>
       <c r="N2" s="19">
-        <f t="shared" si="0"/>
+        <f>AN2*SUM($H2:$J2)/100</f>
         <v>264.15199999999999</v>
       </c>
       <c r="O2" s="20">
         <v>465</v>
       </c>
       <c r="P2" s="20">
+        <v>341</v>
+      </c>
+      <c r="Q2" s="20">
         <v>194</v>
-      </c>
-      <c r="Q2" s="20">
-        <v>341</v>
       </c>
       <c r="R2" s="13">
         <v>250</v>
@@ -1742,58 +1742,24 @@
         <v>485.09999999999997</v>
       </c>
       <c r="BE2" s="13">
-        <f t="shared" ref="BE2" si="1">1000-SUM(BA2:BD2)</f>
+        <f t="shared" ref="BE2" si="0">1000-SUM(BA2:BD2)</f>
         <v>27.701620000000048</v>
       </c>
       <c r="BF2" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="BG2" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="BG2" s="15" t="s">
+      <c r="BH2" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="BH2" s="15" t="s">
-        <v>183</v>
-      </c>
       <c r="BI2" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="BJ2" s="15"/>
       <c r="BK2" s="15"/>
       <c r="BL2" s="15"/>
-    </row>
-    <row r="3" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="AV3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AW3">
-        <v>230</v>
-      </c>
-      <c r="AX3">
-        <v>240</v>
-      </c>
-      <c r="AY3">
-        <v>288</v>
-      </c>
-      <c r="AZ3">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="4" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="AV4" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW4">
-        <v>266</v>
-      </c>
-      <c r="AX4">
-        <v>389</v>
-      </c>
-      <c r="AY4">
-        <v>124</v>
-      </c>
-      <c r="AZ4">
-        <v>221</v>
-      </c>
     </row>
     <row r="6" spans="1:64" x14ac:dyDescent="0.25">
       <c r="M6" s="1"/>
@@ -1867,25 +1833,25 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" t="s">
         <v>146</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>147</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>148</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>149</v>
       </c>
-      <c r="F1" t="s">
-        <v>150</v>
-      </c>
       <c r="G1" t="s">
+        <v>167</v>
+      </c>
+      <c r="H1" t="s">
         <v>168</v>
-      </c>
-      <c r="H1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1893,7 +1859,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>48.51</v>
@@ -1904,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1913,13 +1879,13 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F3">
         <v>31.37</v>
       </c>
       <c r="G3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1927,7 +1893,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1936,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F4">
         <v>14.6</v>
       </c>
       <c r="H4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -1950,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1959,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F5">
         <v>13.83</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1973,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1982,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6">
         <v>9.89</v>
@@ -1993,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2002,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F7">
         <v>7.25</v>
@@ -2013,7 +1979,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2022,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8">
         <v>5.5</v>
@@ -2033,7 +1999,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2042,13 +2008,13 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F9">
         <v>5.47</v>
       </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2056,7 +2022,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2065,13 +2031,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10">
         <v>2.36</v>
       </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2079,7 +2045,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2088,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F11">
         <v>2.35</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2102,7 +2068,7 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2111,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -2122,19 +2088,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F13">
         <v>5.38</v>
       </c>
       <c r="H13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2120,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>6</v>
@@ -2190,15 +2156,15 @@
         <v>1</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2">
         <f t="shared" ref="B2:B12" si="0">B57*B$26</f>
@@ -2254,7 +2220,7 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2">
         <f t="shared" si="0"/>
@@ -2310,7 +2276,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2">
         <f t="shared" si="0"/>
@@ -2367,7 +2333,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2">
         <f t="shared" si="0"/>
@@ -2424,7 +2390,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2">
         <f t="shared" si="0"/>
@@ -2481,7 +2447,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2">
         <f t="shared" si="0"/>
@@ -2538,7 +2504,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2">
         <f t="shared" si="0"/>
@@ -2595,7 +2561,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" s="2">
         <f t="shared" si="0"/>
@@ -2652,7 +2618,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2">
         <f t="shared" si="0"/>
@@ -2709,7 +2675,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="2">
         <f t="shared" si="0"/>
@@ -2766,7 +2732,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" s="2">
         <f t="shared" si="0"/>
@@ -2823,40 +2789,40 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="J13" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -2899,7 +2865,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15" s="3">
         <v>50</v>
@@ -2937,7 +2903,7 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17">
         <v>34264</v>
@@ -2954,7 +2920,7 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18">
         <v>38805</v>
@@ -2971,7 +2937,7 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20">
         <v>46310</v>
@@ -3009,7 +2975,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21">
         <v>48010</v>
@@ -3047,7 +3013,7 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23">
         <v>0.92400000000000004</v>
@@ -3085,7 +3051,7 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24">
         <v>0.92400000000000004</v>
@@ -3123,7 +3089,7 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="4">
         <f>B21*B24/(B20*B23)</f>
@@ -3172,7 +3138,7 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G27" s="4">
         <f>G18/G17</f>
@@ -3193,7 +3159,7 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" s="4">
         <f>G27*G26</f>
@@ -3214,114 +3180,114 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
         <v>49</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>50</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>51</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>52</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>53</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>54</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>55</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>56</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30" t="s">
         <v>57</v>
       </c>
-      <c r="K30" t="s">
-        <v>93</v>
-      </c>
-      <c r="L30" t="s">
-        <v>58</v>
-      </c>
       <c r="M30" t="s">
+        <v>69</v>
+      </c>
+      <c r="N30" t="s">
         <v>70</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>71</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>72</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>73</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>74</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>75</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>76</v>
       </c>
-      <c r="T30" t="s">
+      <c r="U30" t="s">
         <v>77</v>
       </c>
-      <c r="U30" t="s">
+      <c r="V30" t="s">
         <v>78</v>
       </c>
-      <c r="V30" t="s">
+      <c r="W30" t="s">
         <v>79</v>
       </c>
-      <c r="W30" t="s">
+      <c r="X30" t="s">
         <v>80</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>81</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Z30" t="s">
         <v>82</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AA30" t="s">
         <v>83</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AB30" t="s">
         <v>84</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>85</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AD30" t="s">
         <v>86</v>
       </c>
-      <c r="AD30" t="s">
+      <c r="AE30" t="s">
         <v>87</v>
       </c>
-      <c r="AE30" t="s">
+      <c r="AF30" t="s">
         <v>88</v>
       </c>
-      <c r="AF30" t="s">
+      <c r="AG30" t="s">
         <v>89</v>
       </c>
-      <c r="AG30" t="s">
+      <c r="AH30" t="s">
         <v>90</v>
       </c>
-      <c r="AH30" t="s">
+      <c r="AI30" t="s">
         <v>91</v>
-      </c>
-      <c r="AI30" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" s="2">
         <v>13520</v>
@@ -3429,7 +3395,7 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" s="2">
         <v>17520</v>
@@ -3537,7 +3503,7 @@
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2">
         <v>19264.754000000001</v>
@@ -3645,7 +3611,7 @@
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" s="2">
         <v>20998.017</v>
@@ -3753,7 +3719,7 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2">
         <v>24302.13</v>
@@ -3861,7 +3827,7 @@
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="2">
         <v>27593.96</v>
@@ -3969,7 +3935,7 @@
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B37" s="2">
         <v>31342.97</v>
@@ -4077,7 +4043,7 @@
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B38" s="2">
         <v>35951.42</v>
@@ -4185,7 +4151,7 @@
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" s="2">
         <v>38800.160000000003</v>
@@ -4293,7 +4259,7 @@
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" s="2">
         <v>42463.88</v>
@@ -4401,7 +4367,7 @@
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" s="2">
         <v>55180.92</v>
@@ -4509,114 +4475,114 @@
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" t="s">
         <v>49</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>50</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>51</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>52</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>53</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>54</v>
       </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>55</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>56</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
+        <v>92</v>
+      </c>
+      <c r="L43" t="s">
         <v>57</v>
       </c>
-      <c r="K43" t="s">
-        <v>93</v>
-      </c>
-      <c r="L43" t="s">
-        <v>58</v>
-      </c>
       <c r="M43" t="s">
+        <v>69</v>
+      </c>
+      <c r="N43" t="s">
         <v>70</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>71</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>72</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>73</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>74</v>
       </c>
-      <c r="R43" t="s">
+      <c r="S43" t="s">
         <v>75</v>
       </c>
-      <c r="S43" t="s">
+      <c r="T43" t="s">
         <v>76</v>
       </c>
-      <c r="T43" t="s">
+      <c r="U43" t="s">
         <v>77</v>
       </c>
-      <c r="U43" t="s">
+      <c r="V43" t="s">
         <v>78</v>
       </c>
-      <c r="V43" t="s">
+      <c r="W43" t="s">
         <v>79</v>
       </c>
-      <c r="W43" t="s">
+      <c r="X43" t="s">
         <v>80</v>
       </c>
-      <c r="X43" t="s">
+      <c r="Y43" t="s">
         <v>81</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="Z43" t="s">
         <v>82</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AA43" t="s">
         <v>83</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AB43" t="s">
         <v>84</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>85</v>
       </c>
-      <c r="AC43" t="s">
+      <c r="AD43" t="s">
         <v>86</v>
       </c>
-      <c r="AD43" t="s">
+      <c r="AE43" t="s">
         <v>87</v>
       </c>
-      <c r="AE43" t="s">
+      <c r="AF43" t="s">
         <v>88</v>
       </c>
-      <c r="AF43" t="s">
+      <c r="AG43" t="s">
         <v>89</v>
       </c>
-      <c r="AG43" t="s">
+      <c r="AH43" t="s">
         <v>90</v>
       </c>
-      <c r="AH43" t="s">
+      <c r="AI43" t="s">
         <v>91</v>
-      </c>
-      <c r="AI43" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="2">
         <v>12473.913</v>
@@ -4721,7 +4687,7 @@
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" s="2">
         <v>15726.666999999999</v>
@@ -4826,7 +4792,7 @@
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" s="2">
         <v>17220</v>
@@ -4931,7 +4897,7 @@
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B47" s="2">
         <v>18506.667000000001</v>
@@ -5036,7 +5002,7 @@
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="2">
         <v>20925</v>
@@ -5141,7 +5107,7 @@
     </row>
     <row r="49" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="2">
         <v>23300</v>
@@ -5246,7 +5212,7 @@
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B50" s="2">
         <v>25960</v>
@@ -5351,7 +5317,7 @@
     </row>
     <row r="51" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="2">
         <v>29268</v>
@@ -5456,7 +5422,7 @@
     </row>
     <row r="52" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2">
         <v>31220</v>
@@ -5561,7 +5527,7 @@
     </row>
     <row r="53" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="2">
         <v>33740</v>
@@ -5666,7 +5632,7 @@
     </row>
     <row r="54" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="2">
         <v>41905.56</v>
@@ -5771,42 +5737,42 @@
     </row>
     <row r="56" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
         <v>106</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>107</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>108</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>109</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" t="s">
         <v>110</v>
       </c>
-      <c r="F56" t="s">
+      <c r="J56" t="s">
+        <v>126</v>
+      </c>
+      <c r="K56" t="s">
+        <v>141</v>
+      </c>
+      <c r="L56" t="s">
         <v>122</v>
       </c>
-      <c r="H56" t="s">
-        <v>111</v>
-      </c>
-      <c r="J56" t="s">
-        <v>127</v>
-      </c>
-      <c r="K56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L56" t="s">
+      <c r="M56" t="s">
         <v>123</v>
-      </c>
-      <c r="M56" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57">
         <v>12537</v>
@@ -5836,7 +5802,7 @@
     </row>
     <row r="58" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58">
         <v>16009</v>
@@ -5865,7 +5831,7 @@
     </row>
     <row r="59" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59">
         <v>17502</v>
@@ -5894,7 +5860,7 @@
     </row>
     <row r="60" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60">
         <v>18952</v>
@@ -5923,7 +5889,7 @@
     </row>
     <row r="61" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <v>21557</v>
@@ -5952,7 +5918,7 @@
     </row>
     <row r="62" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62">
         <v>24179</v>
@@ -5981,7 +5947,7 @@
     </row>
     <row r="63" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63">
         <v>27006</v>
@@ -6010,7 +5976,7 @@
     </row>
     <row r="64" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64">
         <v>30635</v>
@@ -6039,7 +6005,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65">
         <v>32816</v>
@@ -6068,7 +6034,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66">
         <v>35361</v>
@@ -6097,7 +6063,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67">
         <v>44071</v>
@@ -6126,7 +6092,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B69" t="s">
         <v>6</v>
@@ -6162,15 +6128,15 @@
         <v>1</v>
       </c>
       <c r="M69" t="s">
+        <v>111</v>
+      </c>
+      <c r="N69" t="s">
         <v>112</v>
-      </c>
-      <c r="N69" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="2">
         <v>6078.1</v>
@@ -6214,7 +6180,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B71" s="2">
         <v>17930.400000000001</v>
@@ -6258,7 +6224,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B72" s="2">
         <v>20676.7</v>
@@ -6302,7 +6268,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B73" s="2">
         <v>23351.3</v>
@@ -6346,7 +6312,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B74" s="2">
         <v>30297.4</v>
@@ -6390,7 +6356,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75" s="2">
         <v>37074.9</v>
@@ -6434,7 +6400,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B76" s="2">
         <v>43624.800000000003</v>
@@ -6478,7 +6444,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B77" s="2">
         <v>50815.3</v>
@@ -6522,7 +6488,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B78" s="2">
         <v>55410.9</v>
@@ -6566,7 +6532,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B79" s="2">
         <v>60296.4</v>
@@ -6610,7 +6576,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B80" s="2">
         <v>81117.100000000006</v>
